--- a/fixtures/isa_identity_left_in.xlsx
+++ b/fixtures/isa_identity_left_in.xlsx
@@ -549,11 +549,11 @@
       <c r="D2" t="str">
         <v/>
       </c>
-      <c r="E2" t="str">
-        <v/>
+      <c r="E2">
+        <v>1.33</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G2" t="str">
         <v>B</v>
@@ -580,7 +580,7 @@
         <v>A</v>
       </c>
       <c r="O2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P2" t="str">
         <v>A</v>
@@ -589,43 +589,43 @@
         <v>B</v>
       </c>
       <c r="R2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="S2" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="T2" t="str">
         <v>A</v>
       </c>
       <c r="U2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="V2" t="str">
         <v>A</v>
       </c>
       <c r="W2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="X2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Y2" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="Z2" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AA2" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AB2" t="str">
         <v>A</v>
       </c>
       <c r="AC2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AD2" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AE2" t="str">
         <v>B</v>
@@ -640,13 +640,13 @@
         <v>A</v>
       </c>
       <c r="AI2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AJ2" t="str">
         <v>B</v>
       </c>
       <c r="AK2" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -664,10 +664,10 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2">
         <v>0</v>
@@ -686,11 +686,11 @@
       <c r="D3" t="str">
         <v/>
       </c>
-      <c r="E3" t="str">
-        <v/>
+      <c r="E3">
+        <v>3.87</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G3" t="str">
         <v>A</v>
@@ -711,7 +711,7 @@
         <v>A</v>
       </c>
       <c r="M3" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="N3" t="str">
         <v>C</v>
@@ -720,64 +720,64 @@
         <v>D</v>
       </c>
       <c r="P3" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="Q3" t="str">
         <v>B</v>
       </c>
       <c r="R3" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="S3" t="str">
         <v>C</v>
       </c>
       <c r="T3" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="U3" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="V3" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="W3" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="X3" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="Y3" t="str">
         <v>A</v>
       </c>
       <c r="Z3" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AA3" t="str">
         <v>B</v>
       </c>
       <c r="AB3" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AC3" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AD3" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AE3" t="str">
         <v>A</v>
       </c>
       <c r="AF3" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AG3" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="AH3" t="str">
         <v>C</v>
       </c>
       <c r="AI3" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AJ3" t="str">
         <v>B</v>
@@ -789,25 +789,25 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3">
         <v>2</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
         <v>2</v>
       </c>
-      <c r="AQ3">
-        <v>1</v>
-      </c>
       <c r="AR3">
         <v>1</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -823,98 +823,98 @@
       <c r="D4" t="str">
         <v/>
       </c>
-      <c r="E4" t="str">
-        <v/>
+      <c r="E4">
+        <v>1.93</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="H4" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="I4" t="str">
         <v>A</v>
       </c>
       <c r="J4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="K4" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="L4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="M4" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="N4" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="O4" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="P4" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="Q4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="R4" t="str">
         <v>B</v>
       </c>
       <c r="S4" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="T4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="U4" t="str">
         <v>A</v>
       </c>
       <c r="V4" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="W4" t="str">
         <v>A</v>
       </c>
       <c r="X4" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="Y4" t="str">
         <v>B</v>
       </c>
       <c r="Z4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AA4" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AB4" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AC4" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AD4" t="str">
         <v>B</v>
       </c>
       <c r="AE4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AF4" t="str">
         <v>A</v>
       </c>
       <c r="AG4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AH4" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AI4" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AJ4" t="str">
         <v>B</v>
@@ -923,25 +923,25 @@
         <v>A</v>
       </c>
       <c r="AL4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS4">
         <v>0</v>
@@ -960,17 +960,17 @@
       <c r="D5" t="str">
         <v/>
       </c>
-      <c r="E5" t="str">
-        <v/>
+      <c r="E5">
+        <v>1.27</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G5" t="str">
         <v>B</v>
       </c>
       <c r="H5" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="I5" t="str">
         <v>B</v>
@@ -982,43 +982,43 @@
         <v>A</v>
       </c>
       <c r="L5" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="M5" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="N5" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="O5" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="P5" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Q5" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="R5" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="S5" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="T5" t="str">
         <v>A</v>
       </c>
       <c r="U5" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="V5" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="W5" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="X5" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="Y5" t="str">
         <v>B</v>
@@ -1030,13 +1030,13 @@
         <v>A</v>
       </c>
       <c r="AB5" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AC5" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AD5" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AE5" t="str">
         <v>B</v>
@@ -1060,7 +1060,7 @@
         <v>A</v>
       </c>
       <c r="AL5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="AS5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1097,11 +1097,11 @@
       <c r="D6" t="str">
         <v/>
       </c>
-      <c r="E6" t="str">
-        <v/>
+      <c r="E6">
+        <v>3</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G6" t="str">
         <v>A</v>
@@ -1167,19 +1167,19 @@
         <v>C</v>
       </c>
       <c r="AB6" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AC6" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AD6" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AE6" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AF6" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AG6" t="str">
         <v>B</v>
@@ -1188,7 +1188,7 @@
         <v>C</v>
       </c>
       <c r="AI6" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="AJ6" t="str">
         <v>B</v>
@@ -1197,7 +1197,7 @@
         <v>A</v>
       </c>
       <c r="AL6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6">
         <v>1</v>
@@ -1206,19 +1206,19 @@
         <v>2</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP6">
         <v>0</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
       </c>
       <c r="AS6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1234,11 +1234,11 @@
       <c r="D7" t="str">
         <v/>
       </c>
-      <c r="E7" t="str">
-        <v/>
+      <c r="E7">
+        <v>1.93</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G7" t="str">
         <v>A</v>
@@ -1247,19 +1247,19 @@
         <v>D</v>
       </c>
       <c r="I7" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="J7" t="str">
         <v>B</v>
       </c>
       <c r="K7" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="L7" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="M7" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N7" t="str">
         <v>C</v>
@@ -1271,28 +1271,28 @@
         <v>A</v>
       </c>
       <c r="Q7" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="R7" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="S7" t="str">
         <v>A</v>
       </c>
       <c r="T7" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="U7" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="V7" t="str">
         <v>A</v>
       </c>
       <c r="W7" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="X7" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="Y7" t="str">
         <v>B</v>
@@ -1301,49 +1301,49 @@
         <v>B</v>
       </c>
       <c r="AA7" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AB7" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AC7" t="str">
         <v>A</v>
       </c>
       <c r="AD7" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AE7" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AF7" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AG7" t="str">
         <v>A</v>
       </c>
       <c r="AH7" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AI7" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AJ7" t="str">
         <v>A</v>
       </c>
       <c r="AK7" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AL7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7">
         <v>1</v>
       </c>
       <c r="AN7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -1371,59 +1371,59 @@
       <c r="D8" t="str">
         <v/>
       </c>
-      <c r="E8" t="str">
-        <v/>
+      <c r="E8">
+        <v>1.87</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G8" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="H8" t="str">
         <v>D</v>
       </c>
       <c r="I8" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="J8" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K8" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="L8" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="M8" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="N8" t="str">
         <v>A</v>
       </c>
       <c r="O8" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P8" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="Q8" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="R8" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="S8" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="T8" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="U8" t="str">
         <v>A</v>
       </c>
       <c r="V8" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="W8" t="str">
         <v>C</v>
@@ -1435,7 +1435,7 @@
         <v>A</v>
       </c>
       <c r="Z8" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AA8" t="str">
         <v>A</v>
@@ -1456,25 +1456,25 @@
         <v>A</v>
       </c>
       <c r="AG8" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AH8" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AI8" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AJ8" t="str">
         <v>B</v>
       </c>
       <c r="AK8" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AL8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -1483,16 +1483,16 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1508,11 +1508,11 @@
       <c r="D9" t="str">
         <v/>
       </c>
-      <c r="E9" t="str">
-        <v/>
+      <c r="E9">
+        <v>4.14</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>L4</v>
       </c>
       <c r="G9" t="str">
         <v>A</v>
@@ -1527,13 +1527,13 @@
         <v>B</v>
       </c>
       <c r="K9" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="L9" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="M9" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="N9" t="str">
         <v>C</v>
@@ -1542,19 +1542,19 @@
         <v>D</v>
       </c>
       <c r="P9" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="Q9" t="str">
         <v>B</v>
       </c>
       <c r="R9" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="S9" t="str">
         <v>C</v>
       </c>
       <c r="T9" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="U9" t="str">
         <v>B</v>
@@ -1623,13 +1623,13 @@
         <v>2</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>1</v>
       </c>
       <c r="AS9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1645,23 +1645,23 @@
       <c r="D10" t="str">
         <v/>
       </c>
-      <c r="E10" t="str">
-        <v/>
+      <c r="E10">
+        <v>3.2</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G10" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="H10" t="str">
         <v>D</v>
       </c>
       <c r="I10" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="J10" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K10" t="str">
         <v>C</v>
@@ -1673,7 +1673,7 @@
         <v>A</v>
       </c>
       <c r="N10" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="O10" t="str">
         <v>D</v>
@@ -1682,13 +1682,13 @@
         <v>C</v>
       </c>
       <c r="Q10" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="R10" t="str">
         <v>B</v>
       </c>
       <c r="S10" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="T10" t="str">
         <v>B</v>
@@ -1700,13 +1700,13 @@
         <v>D</v>
       </c>
       <c r="W10" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="X10" t="str">
         <v>D</v>
       </c>
       <c r="Y10" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Z10" t="str">
         <v>A</v>
@@ -1718,25 +1718,25 @@
         <v>A</v>
       </c>
       <c r="AC10" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AD10" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AE10" t="str">
         <v>A</v>
       </c>
       <c r="AF10" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AG10" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AH10" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AI10" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AJ10" t="str">
         <v>B</v>
@@ -1751,11 +1751,11 @@
         <v>1</v>
       </c>
       <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
         <v>2</v>
       </c>
-      <c r="AO10">
-        <v>1</v>
-      </c>
       <c r="AP10">
         <v>0</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10">
         <v>1</v>
@@ -1782,20 +1782,20 @@
       <c r="D11" t="str">
         <v/>
       </c>
-      <c r="E11" t="str">
-        <v/>
+      <c r="E11">
+        <v>1.67</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G11" t="str">
         <v>A</v>
       </c>
       <c r="H11" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="I11" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="J11" t="str">
         <v>A</v>
@@ -1807,25 +1807,25 @@
         <v>A</v>
       </c>
       <c r="M11" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="N11" t="str">
         <v>C</v>
       </c>
       <c r="O11" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P11" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="Q11" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="R11" t="str">
         <v>A</v>
       </c>
       <c r="S11" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="T11" t="str">
         <v>A</v>
@@ -1846,19 +1846,19 @@
         <v>B</v>
       </c>
       <c r="Z11" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AA11" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AB11" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AC11" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AD11" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AE11" t="str">
         <v>B</v>
@@ -1867,19 +1867,19 @@
         <v>A</v>
       </c>
       <c r="AG11" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AH11" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AI11" t="str">
         <v>A</v>
       </c>
       <c r="AJ11" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AK11" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -1919,11 +1919,11 @@
       <c r="D12" t="str">
         <v/>
       </c>
-      <c r="E12" t="str">
-        <v/>
+      <c r="E12">
+        <v>2.56</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>L2</v>
       </c>
       <c r="G12" t="str">
         <v>A</v>
@@ -2056,11 +2056,11 @@
       <c r="D13" t="str">
         <v/>
       </c>
-      <c r="E13" t="str">
-        <v/>
+      <c r="E13">
+        <v>4.07</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>L4</v>
       </c>
       <c r="G13" t="str">
         <v>A</v>
@@ -2069,22 +2069,22 @@
         <v>D</v>
       </c>
       <c r="I13" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="J13" t="str">
         <v>B</v>
       </c>
       <c r="K13" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="L13" t="str">
         <v>D</v>
       </c>
       <c r="M13" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N13" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="O13" t="str">
         <v>D</v>
@@ -2096,7 +2096,7 @@
         <v>B</v>
       </c>
       <c r="R13" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="S13" t="str">
         <v>C</v>
@@ -2111,7 +2111,7 @@
         <v>D</v>
       </c>
       <c r="W13" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="X13" t="str">
         <v>D</v>
@@ -2129,7 +2129,7 @@
         <v>D</v>
       </c>
       <c r="AC13" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AD13" t="str">
         <v>A</v>
@@ -2144,19 +2144,19 @@
         <v>B</v>
       </c>
       <c r="AH13" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AI13" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AJ13" t="str">
         <v>B</v>
       </c>
       <c r="AK13" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AL13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM13">
         <v>1</v>
@@ -2165,19 +2165,19 @@
         <v>2</v>
       </c>
       <c r="AO13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP13">
         <v>2</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2193,11 +2193,11 @@
       <c r="D14" t="str">
         <v/>
       </c>
-      <c r="E14" t="str">
-        <v/>
+      <c r="E14">
+        <v>3.33</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G14" t="str">
         <v>A</v>
@@ -2212,16 +2212,16 @@
         <v>A</v>
       </c>
       <c r="K14" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="L14" t="str">
         <v>D</v>
       </c>
       <c r="M14" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N14" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="O14" t="str">
         <v>D</v>
@@ -2230,31 +2230,31 @@
         <v>C</v>
       </c>
       <c r="Q14" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="R14" t="str">
         <v>B</v>
       </c>
       <c r="S14" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="T14" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="U14" t="str">
         <v>B</v>
       </c>
       <c r="V14" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="W14" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="X14" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="Y14" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="Z14" t="str">
         <v>A</v>
@@ -2266,7 +2266,7 @@
         <v>D</v>
       </c>
       <c r="AC14" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AD14" t="str">
         <v>A</v>
@@ -2275,13 +2275,13 @@
         <v>A</v>
       </c>
       <c r="AF14" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AG14" t="str">
         <v>B</v>
       </c>
       <c r="AH14" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AI14" t="str">
         <v>B</v>
@@ -2290,22 +2290,22 @@
         <v>B</v>
       </c>
       <c r="AK14" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
         <v>1</v>
@@ -2330,11 +2330,11 @@
       <c r="D15" t="str">
         <v/>
       </c>
-      <c r="E15" t="str">
-        <v/>
+      <c r="E15">
+        <v>3.73</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G15" t="str">
         <v>A</v>
@@ -2352,13 +2352,13 @@
         <v>C</v>
       </c>
       <c r="L15" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="M15" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N15" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="O15" t="str">
         <v>D</v>
@@ -2370,7 +2370,7 @@
         <v>B</v>
       </c>
       <c r="R15" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="S15" t="str">
         <v>C</v>
@@ -2397,13 +2397,13 @@
         <v>A</v>
       </c>
       <c r="AA15" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AB15" t="str">
         <v>D</v>
       </c>
       <c r="AC15" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="AD15" t="str">
         <v>A</v>
@@ -2418,7 +2418,7 @@
         <v>B</v>
       </c>
       <c r="AH15" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AI15" t="str">
         <v>B</v>
@@ -2430,28 +2430,28 @@
         <v>A</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15">
         <v>1</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
         <v>2</v>
-      </c>
-      <c r="AR15">
-        <v>2</v>
-      </c>
-      <c r="AS15">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2467,11 +2467,11 @@
       <c r="D16" t="str">
         <v/>
       </c>
-      <c r="E16" t="str">
-        <v/>
+      <c r="E16">
+        <v>3.73</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G16" t="str">
         <v>A</v>
@@ -2483,13 +2483,13 @@
         <v>A</v>
       </c>
       <c r="J16" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="K16" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="L16" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="M16" t="str">
         <v>A</v>
@@ -2501,31 +2501,31 @@
         <v>D</v>
       </c>
       <c r="P16" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="Q16" t="str">
         <v>B</v>
       </c>
       <c r="R16" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="S16" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="T16" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="U16" t="str">
         <v>B</v>
       </c>
       <c r="V16" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="W16" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="X16" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="Y16" t="str">
         <v>A</v>
@@ -2534,28 +2534,28 @@
         <v>A</v>
       </c>
       <c r="AA16" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AB16" t="str">
         <v>D</v>
       </c>
       <c r="AC16" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AD16" t="str">
         <v>A</v>
       </c>
       <c r="AE16" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AF16" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AG16" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AH16" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AI16" t="str">
         <v>A</v>
@@ -2573,22 +2573,22 @@
         <v>1</v>
       </c>
       <c r="AN16">
+        <v>1</v>
+      </c>
+      <c r="AO16">
+        <v>1</v>
+      </c>
+      <c r="AP16">
+        <v>1</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>1</v>
+      </c>
+      <c r="AS16">
         <v>2</v>
-      </c>
-      <c r="AO16">
-        <v>1</v>
-      </c>
-      <c r="AP16">
-        <v>1</v>
-      </c>
-      <c r="AQ16">
-        <v>1</v>
-      </c>
-      <c r="AR16">
-        <v>1</v>
-      </c>
-      <c r="AS16">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2604,11 +2604,11 @@
       <c r="D17" t="str">
         <v/>
       </c>
-      <c r="E17" t="str">
-        <v/>
+      <c r="E17">
+        <v>1.6</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G17" t="str">
         <v>B</v>
@@ -2617,43 +2617,43 @@
         <v>D</v>
       </c>
       <c r="I17" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="J17" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K17" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="L17" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="M17" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="N17" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="O17" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P17" t="str">
         <v>A</v>
       </c>
       <c r="Q17" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="R17" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="S17" t="str">
         <v>C</v>
       </c>
       <c r="T17" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="U17" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="V17" t="str">
         <v>A</v>
@@ -2662,22 +2662,22 @@
         <v>B</v>
       </c>
       <c r="X17" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="Y17" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="Z17" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AA17" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AB17" t="str">
         <v>A</v>
       </c>
       <c r="AC17" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AD17" t="str">
         <v>A</v>
@@ -2686,22 +2686,22 @@
         <v>B</v>
       </c>
       <c r="AF17" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AG17" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AH17" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AI17" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AJ17" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AK17" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2713,13 +2713,13 @@
         <v>0</v>
       </c>
       <c r="AO17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -2741,80 +2741,80 @@
       <c r="D18" t="str">
         <v/>
       </c>
-      <c r="E18" t="str">
-        <v/>
+      <c r="E18">
+        <v>1.07</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G18" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="H18" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="I18" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="J18" t="str">
         <v>A</v>
       </c>
       <c r="K18" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="L18" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="M18" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N18" t="str">
         <v>A</v>
       </c>
       <c r="O18" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P18" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="Q18" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="R18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="S18" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="T18" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="U18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="V18" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="W18" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="X18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Y18" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="Z18" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AA18" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AB18" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AC18" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AD18" t="str">
         <v>C</v>
@@ -2826,28 +2826,28 @@
         <v>A</v>
       </c>
       <c r="AG18" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AH18" t="str">
         <v>A</v>
       </c>
       <c r="AI18" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AJ18" t="str">
         <v>A</v>
       </c>
       <c r="AK18" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -2856,13 +2856,13 @@
         <v>0</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2878,17 +2878,17 @@
       <c r="D19" t="str">
         <v/>
       </c>
-      <c r="E19" t="str">
-        <v/>
+      <c r="E19">
+        <v>1.4</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G19" t="str">
         <v>B</v>
       </c>
       <c r="H19" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="I19" t="str">
         <v>A</v>
@@ -2897,52 +2897,52 @@
         <v>B</v>
       </c>
       <c r="K19" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="L19" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="M19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="O19" t="str">
         <v>A</v>
       </c>
       <c r="P19" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="Q19" t="str">
         <v>B</v>
       </c>
       <c r="R19" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="S19" t="str">
         <v>A</v>
       </c>
       <c r="T19" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="U19" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="V19" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="W19" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="X19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="Y19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="Z19" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AA19" t="str">
         <v>A</v>
@@ -2951,22 +2951,22 @@
         <v>D</v>
       </c>
       <c r="AC19" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AD19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AE19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AF19" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AG19" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AH19" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AI19" t="str">
         <v>A</v>
@@ -2975,31 +2975,31 @@
         <v>A</v>
       </c>
       <c r="AK19" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP19">
         <v>0</v>
       </c>
       <c r="AQ19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR19">
         <v>0</v>
       </c>
       <c r="AS19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3015,14 +3015,14 @@
       <c r="D20" t="str">
         <v/>
       </c>
-      <c r="E20" t="str">
-        <v/>
+      <c r="E20">
+        <v>1.93</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G20" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="H20" t="str">
         <v>D</v>
@@ -3031,40 +3031,40 @@
         <v>A</v>
       </c>
       <c r="J20" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K20" t="str">
         <v>C</v>
       </c>
       <c r="L20" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="M20" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N20" t="str">
         <v>A</v>
       </c>
       <c r="O20" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="P20" t="str">
         <v>A</v>
       </c>
       <c r="Q20" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="R20" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="S20" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="T20" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="U20" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="V20" t="str">
         <v>A</v>
@@ -3073,10 +3073,10 @@
         <v>C</v>
       </c>
       <c r="X20" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="Y20" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="Z20" t="str">
         <v>A</v>
@@ -3097,46 +3097,46 @@
         <v>B</v>
       </c>
       <c r="AF20" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AG20" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AH20" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AI20" t="str">
         <v>B</v>
       </c>
       <c r="AJ20" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AK20" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AL20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM20">
         <v>1</v>
       </c>
       <c r="AN20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
         <v>1</v>
       </c>
       <c r="AR20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3152,14 +3152,14 @@
       <c r="D21" t="str">
         <v/>
       </c>
-      <c r="E21" t="str">
-        <v/>
+      <c r="E21">
+        <v>1.67</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G21" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="H21" t="str">
         <v>D</v>
@@ -3171,61 +3171,61 @@
         <v>B</v>
       </c>
       <c r="K21" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="L21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="M21" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="N21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="O21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P21" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="Q21" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="R21" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="S21" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="T21" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="U21" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="V21" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="W21" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="X21" t="str">
         <v>A</v>
       </c>
       <c r="Y21" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="Z21" t="str">
         <v>A</v>
       </c>
       <c r="AA21" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AB21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AC21" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AD21" t="str">
         <v>A</v>
@@ -3234,19 +3234,19 @@
         <v>B</v>
       </c>
       <c r="AF21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AG21" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AH21" t="str">
         <v>A</v>
       </c>
       <c r="AI21" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AJ21" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AK21" t="str">
         <v>A</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21">
         <v>1</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP21">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="AS21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3289,32 +3289,32 @@
       <c r="D22" t="str">
         <v/>
       </c>
-      <c r="E22" t="str">
-        <v/>
+      <c r="E22">
+        <v>2.89</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>L2</v>
       </c>
       <c r="G22" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="H22" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="I22" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="J22" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="K22" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="L22" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="M22" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="N22" t="str">
         <v>A</v>
@@ -3326,43 +3326,43 @@
         <v>C</v>
       </c>
       <c r="Q22" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="R22" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="S22" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="T22" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="U22" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="V22" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="W22" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="X22" t="str">
         <v>A</v>
       </c>
       <c r="Y22" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="Z22" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AA22" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AB22" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AC22" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AD22" t="str">
         <v>A</v>
@@ -3371,22 +3371,22 @@
         <v>B</v>
       </c>
       <c r="AF22" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AG22" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AH22" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="AI22" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="AJ22" t="str">
         <v>B</v>
       </c>
       <c r="AK22" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -3426,128 +3426,128 @@
       <c r="D23" t="str">
         <v/>
       </c>
-      <c r="E23" t="str">
-        <v/>
+      <c r="E23">
+        <v>1.27</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>L1</v>
       </c>
       <c r="G23" t="str">
         <v>A</v>
       </c>
       <c r="H23" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="I23" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="J23" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="K23" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="L23" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="M23" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="N23" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="O23" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P23" t="str">
         <v>A</v>
       </c>
       <c r="Q23" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="R23" t="str">
         <v>A</v>
       </c>
       <c r="S23" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="T23" t="str">
         <v>A</v>
       </c>
       <c r="U23" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="V23" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="W23" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="X23" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="Y23" t="str">
         <v>B</v>
       </c>
       <c r="Z23" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AA23" t="str">
         <v>A</v>
       </c>
       <c r="AB23" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AC23" t="str">
         <v>A</v>
       </c>
       <c r="AD23" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AE23" t="str">
         <v>B</v>
       </c>
       <c r="AF23" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AG23" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AH23" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AI23" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AJ23" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AK23" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AL23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
       </c>
       <c r="AN23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23">
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR23">
         <v>0</v>
       </c>
       <c r="AS23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3563,14 +3563,14 @@
       <c r="D24" t="str">
         <v/>
       </c>
-      <c r="E24" t="str">
-        <v/>
+      <c r="E24">
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G24" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="H24" t="str">
         <v>D</v>
@@ -3585,34 +3585,34 @@
         <v>C</v>
       </c>
       <c r="L24" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="M24" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="N24" t="str">
         <v>C</v>
       </c>
       <c r="O24" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="P24" t="str">
         <v>C</v>
       </c>
       <c r="Q24" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="R24" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="S24" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="T24" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="U24" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="V24" t="str">
         <v>A</v>
@@ -3621,7 +3621,7 @@
         <v>C</v>
       </c>
       <c r="X24" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="Y24" t="str">
         <v>A</v>
@@ -3633,58 +3633,58 @@
         <v>C</v>
       </c>
       <c r="AB24" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AC24" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="AD24" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AE24" t="str">
         <v>B</v>
       </c>
       <c r="AF24" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="AG24" t="str">
         <v>B</v>
       </c>
       <c r="AH24" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AI24" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="AJ24" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AK24" t="str">
         <v>D</v>
       </c>
       <c r="AL24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24">
         <v>1</v>
       </c>
       <c r="AN24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1</v>
       </c>
       <c r="AR24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3700,11 +3700,11 @@
       <c r="D25" t="str">
         <v/>
       </c>
-      <c r="E25" t="str">
-        <v/>
+      <c r="E25">
+        <v>3.53</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>L3</v>
       </c>
       <c r="G25" t="str">
         <v>A</v>
@@ -3713,7 +3713,7 @@
         <v>D</v>
       </c>
       <c r="I25" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="J25" t="str">
         <v>B</v>
@@ -3722,16 +3722,16 @@
         <v>C</v>
       </c>
       <c r="L25" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="M25" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="N25" t="str">
         <v>C</v>
       </c>
       <c r="O25" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="P25" t="str">
         <v>A</v>
@@ -3740,22 +3740,22 @@
         <v>B</v>
       </c>
       <c r="R25" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="S25" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="T25" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="U25" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="V25" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="W25" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="X25" t="str">
         <v>C</v>
@@ -3764,40 +3764,40 @@
         <v>A</v>
       </c>
       <c r="Z25" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AA25" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AB25" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="AC25" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AD25" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="AE25" t="str">
-        <v>B</v>
+        <v>D</v>
       </c>
       <c r="AF25" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AG25" t="str">
         <v>B</v>
       </c>
       <c r="AH25" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="AI25" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="AJ25" t="str">
         <v>B</v>
       </c>
       <c r="AK25" t="str">
-        <v>A</v>
+        <v>D</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3809,13 +3809,13 @@
         <v>2</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
